--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:11</t>
+          <t>2026-05-08 15:54</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D48" s="10" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>0</v>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>0</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D58" s="10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D60" s="10" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D70" s="10" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D72" s="10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D76" s="10" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D78" s="10" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>0</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D82" s="10" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>0</v>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F84" s="10" t="n">
         <v>0</v>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>0</v>
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F86" s="10" t="n">
         <v>0</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>0</v>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="93">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D94" s="10" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -2823,16 +2823,16 @@
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>0</v>
@@ -2848,16 +2848,16 @@
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D98" s="10" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D100" s="10" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D101" s="7" t="n">
         <v>0</v>
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>0</v>
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E104" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G104" s="10" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G106" s="10" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="E108" s="10" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54</t>
+          <t>2026-05-08 15:56</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -492,9 +492,9 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>
@@ -544,17 +544,17 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Downtime_0_trip_baht</t>
+          <t>Downtime_50_baht</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Downtime_1_trip_baht</t>
+          <t>Downtime_100_baht</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Blank_run_baht</t>
+          <t>Blank_run_50_baht</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -109,7 +109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>0</v>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3638</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D48" s="10" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>0</v>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>0</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D58" s="10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D60" s="10" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D70" s="10" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D72" s="10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D76" s="10" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D78" s="10" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>0</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D82" s="10" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>0</v>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="F84" s="10" t="n">
         <v>0</v>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>0</v>
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="F86" s="10" t="n">
         <v>0</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>0</v>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>6500</v>
+        <v>6546</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="93">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>0</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="E108" s="10" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trips_Pricing_All" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -3138,58 +3138,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C108" s="10" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="D108" s="10" t="n">
-        <v>3716</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="D109" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="E109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G109"/>
+  <autoFilter ref="A4:G107"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trips_Pricing_All" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Trips_Pricing_All" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-06-04 19:42</t>
         </is>
       </c>
     </row>
@@ -565,18 +565,18 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46121</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -590,18 +590,18 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46121</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0</v>
@@ -615,24 +615,24 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46121</v>
+        <v>46144</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -640,24 +640,24 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46122</v>
+        <v>46145</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>0</v>
@@ -665,24 +665,24 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46122</v>
+        <v>46145</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -690,18 +690,18 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
@@ -715,18 +715,18 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0</v>
+        <v>7432</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -740,15 +740,15 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>0</v>
@@ -765,24 +765,24 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3638</v>
+        <v>3716</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -790,18 +790,18 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46123</v>
+        <v>46146</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3425</v>
+        <v>3716</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
@@ -815,18 +815,18 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46123</v>
+        <v>46147</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -840,18 +840,18 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46123</v>
+        <v>46147</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
@@ -865,18 +865,18 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46123</v>
+        <v>46148</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -890,18 +890,18 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46123</v>
+        <v>46148</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>71-8683</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3425</v>
+        <v>0</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0</v>
@@ -915,18 +915,18 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46124</v>
+        <v>46148</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -940,15 +940,15 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46124</v>
+        <v>46148</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>0</v>
@@ -965,18 +965,18 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46124</v>
+        <v>46149</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -990,18 +990,18 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>46124</v>
+        <v>46149</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -1015,18 +1015,18 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46124</v>
+        <v>46149</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
@@ -1040,18 +1040,18 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46124</v>
+        <v>46149</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
@@ -1065,18 +1065,18 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -1090,15 +1090,15 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>0</v>
@@ -1115,18 +1115,18 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46125</v>
+        <v>46150</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
@@ -1140,15 +1140,15 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46125</v>
+        <v>46150</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>0</v>
@@ -1165,18 +1165,18 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46125</v>
+        <v>46150</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -1190,18 +1190,18 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46125</v>
+        <v>46150</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0</v>
@@ -1215,18 +1215,18 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46125</v>
+        <v>46151</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -1240,18 +1240,18 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46125</v>
+        <v>46151</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3653</v>
+        <v>3661</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46125</v>
+        <v>46151</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
@@ -1290,18 +1290,18 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46125</v>
+        <v>46151</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
@@ -1315,15 +1315,15 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46126</v>
+        <v>46151</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -1340,18 +1340,18 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46126</v>
+        <v>46152</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>3653</v>
+        <v>7322</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
@@ -1365,15 +1365,15 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46126</v>
+        <v>46152</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -1390,15 +1390,15 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46126</v>
+        <v>46152</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>0</v>
@@ -1415,18 +1415,18 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46126</v>
+        <v>46152</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0</v>
+        <v>7322</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46126</v>
+        <v>46152</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0</v>
@@ -1465,15 +1465,15 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46126</v>
+        <v>46153</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -1490,18 +1490,18 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46126</v>
+        <v>46153</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
@@ -1515,18 +1515,18 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>0</v>
@@ -1540,15 +1540,15 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -1565,18 +1565,18 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>46127</v>
+        <v>46154</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>0</v>
@@ -1590,18 +1590,18 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46127</v>
+        <v>46154</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0</v>
@@ -1615,15 +1615,15 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>46127</v>
+        <v>46154</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46127</v>
+        <v>46154</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D48" s="10" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>46127</v>
+        <v>46154</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -1690,18 +1690,18 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46127</v>
+        <v>46155</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>3653</v>
+        <v>0</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0</v>
@@ -1715,18 +1715,18 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>46128</v>
+        <v>46155</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -1740,15 +1740,15 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46128</v>
+        <v>46155</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>0</v>
@@ -1765,18 +1765,18 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46128</v>
+        <v>46155</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>3425</v>
+        <v>0</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>0</v>
@@ -1790,15 +1790,15 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46128</v>
+        <v>46155</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>0</v>
@@ -1815,18 +1815,18 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>3425</v>
+        <v>0</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0</v>
@@ -1840,15 +1840,15 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>6849.81</v>
+        <v>7543.52</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>0</v>
@@ -1865,15 +1865,15 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>6849.81</v>
+        <v>7543.52</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0</v>
@@ -1890,18 +1890,18 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
@@ -1915,15 +1915,15 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>6849.81</v>
+        <v>7543.52</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>0</v>
@@ -1940,18 +1940,18 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46129</v>
+        <v>46156</v>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0</v>
@@ -1965,15 +1965,15 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>46129</v>
+        <v>46156</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -1990,18 +1990,18 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>6849.81</v>
+        <v>7543.52</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3323</v>
+        <v>3772</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
@@ -2015,15 +2015,15 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -2040,15 +2040,15 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>6849.81</v>
+        <v>7543.52</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>0</v>
@@ -2065,15 +2065,15 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -2090,15 +2090,15 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46129</v>
+        <v>46158</v>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0</v>
@@ -2115,18 +2115,18 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>46129</v>
+        <v>46158</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>0</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46129</v>
+        <v>46158</v>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>0</v>
@@ -2165,15 +2165,15 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>46129</v>
+        <v>46159</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -2190,15 +2190,15 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46130</v>
+        <v>46159</v>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D70" s="10" t="n">
         <v>0</v>
@@ -2215,15 +2215,15 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>46130</v>
+        <v>46159</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>0</v>
@@ -2240,15 +2240,15 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46130</v>
+        <v>46159</v>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D72" s="10" t="n">
         <v>0</v>
@@ -2265,15 +2265,15 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>46131</v>
+        <v>46159</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -2290,18 +2290,18 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46131</v>
+        <v>46160</v>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>3323</v>
+        <v>0</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>0</v>
@@ -2315,15 +2315,15 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>46131</v>
+        <v>46160</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>0</v>
@@ -2340,18 +2340,18 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46131</v>
+        <v>46160</v>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>0</v>
@@ -2365,15 +2365,15 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>46131</v>
+        <v>46160</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -2390,18 +2390,18 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>0</v>
@@ -2415,18 +2415,18 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>0</v>
@@ -2440,15 +2440,15 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>0</v>
@@ -2465,18 +2465,18 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>0</v>
@@ -2490,15 +2490,15 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="D82" s="10" t="n">
         <v>0</v>
@@ -2515,18 +2515,18 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>0</v>
@@ -2540,21 +2540,21 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>6645.86</v>
+        <v>7543.52</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>6645</v>
+        <v>0</v>
       </c>
       <c r="F84" s="10" t="n">
         <v>0</v>
@@ -2565,21 +2565,21 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>6645</v>
+        <v>0</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>0</v>
@@ -2590,21 +2590,21 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46133</v>
+        <v>46162</v>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>6645</v>
+        <v>0</v>
       </c>
       <c r="F86" s="10" t="n">
         <v>0</v>
@@ -2615,18 +2615,18 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>46133</v>
+        <v>46162</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>0</v>
@@ -2640,18 +2640,18 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>6546</v>
+        <v>0</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>0</v>
@@ -2665,18 +2665,18 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>0</v>
@@ -2690,18 +2690,18 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>0</v>
@@ -2715,18 +2715,18 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>3273</v>
+        <v>3828</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>0</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>0</v>
@@ -2760,23 +2760,23 @@
         <v>0</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>46135</v>
+        <v>46163</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>6546.17</v>
+        <v>7656.67</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>3273</v>
+        <v>0</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>0</v>
@@ -2790,15 +2790,15 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46137</v>
+        <v>46163</v>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D94" s="10" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -2815,24 +2815,24 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>46137</v>
+        <v>46163</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>0</v>
@@ -2840,24 +2840,24 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46137</v>
+        <v>46163</v>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="E96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -2865,18 +2865,18 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>46138</v>
+        <v>46163</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>0</v>
@@ -2890,18 +2890,18 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46138</v>
+        <v>46163</v>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E98" s="10" t="n">
         <v>0</v>
@@ -2915,15 +2915,15 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>46138</v>
+        <v>46164</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>0</v>
@@ -2940,18 +2940,18 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46138</v>
+        <v>46164</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E100" s="10" t="n">
         <v>0</v>
@@ -2965,18 +2965,18 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>46138</v>
+        <v>46164</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>0</v>
+        <v>3828</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>0</v>
@@ -2990,24 +2990,24 @@
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46138</v>
+        <v>46164</v>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>3250</v>
+        <v>7656</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -3015,18 +3015,18 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>46138</v>
+        <v>46164</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>0</v>
@@ -3040,24 +3040,24 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46141</v>
+        <v>46164</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="E104" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G104" s="10" t="n">
         <v>0</v>
@@ -3065,24 +3065,24 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>46141</v>
+        <v>46165</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>0</v>
@@ -3090,24 +3090,24 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>46141</v>
+        <v>46165</v>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="E106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G106" s="10" t="n">
         <v>0</v>
@@ -3115,31 +3115,1306 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>46142</v>
+        <v>46165</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="8" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D114" s="10" t="n">
+        <v>7656</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D120" s="10" t="n">
+        <v>3828</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>7544</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>7544</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D139" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D143" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D147" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D151" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D153" s="7" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E153" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>3772</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D157" s="7" t="n">
+        <v>7544</v>
+      </c>
+      <c r="E157" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="D158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G107"/>
+  <autoFilter ref="A4:G158"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:42</t>
+          <t>2026-06-05 14:46</t>
         </is>
       </c>
     </row>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0</v>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>0</v>
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>7432</v>
+        <v>7378</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>0</v>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>0</v>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>0</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7322</v>
+        <v>7280</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>7322</v>
+        <v>7280</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D48" s="10" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D50" s="10" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0</v>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D70" s="10" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D72" s="10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D74" s="10" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>0</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>0</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D82" s="10" t="n">
         <v>0</v>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E84" s="10" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D88" s="10" t="n">
         <v>0</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D90" s="10" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D92" s="10" t="n">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D94" s="10" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>0</v>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E96" s="10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>0</v>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E98" s="10" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>0</v>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E100" s="10" t="n">
         <v>0</v>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>7656</v>
+        <v>7572</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D103" s="7" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D104" s="10" t="n">
         <v>0</v>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D106" s="10" t="n">
         <v>0</v>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D108" s="10" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D110" s="10" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D112" s="10" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C113" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>7656</v>
+        <v>7572</v>
       </c>
       <c r="E114" s="10" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="C115" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>0</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D116" s="10" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="C117" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D118" s="10" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>0</v>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
       <c r="E120" s="10" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D122" s="10" t="n">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>0</v>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E124" s="10" t="n">
         <v>0</v>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>7544</v>
+        <v>7476</v>
       </c>
       <c r="E125" s="7" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D126" s="10" t="n">
         <v>0</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>7544</v>
+        <v>7476</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D128" s="10" t="n">
         <v>0</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="C129" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E129" s="7" t="n">
         <v>0</v>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E130" s="10" t="n">
         <v>0</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="C131" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E131" s="7" t="n">
         <v>0</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E132" s="10" t="n">
         <v>0</v>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="C133" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E133" s="7" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D134" s="10" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="C135" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>0</v>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E136" s="10" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="C137" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E139" s="7" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D140" s="10" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C141" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>0</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D142" s="10" t="n">
         <v>0</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>0</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D144" s="10" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="C145" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D145" s="7" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D146" s="10" t="n">
         <v>0</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D148" s="10" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C149" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D149" s="7" t="n">
         <v>0</v>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D150" s="10" t="n">
         <v>0</v>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="C151" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="E151" s="7" t="n">
         <v>0</v>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="D152" s="10" t="n">
         <v>0</v>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>0</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
       <c r="E156" s="10" t="n">
         <v>0</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C157" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>7544</v>
+        <v>7378</v>
       </c>
       <c r="E157" s="7" t="n">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="D158" s="10" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:46</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>0</v>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>0</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>0</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>0</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D48" s="10" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D50" s="10" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0</v>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D70" s="10" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D72" s="10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D74" s="10" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>0</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>0</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D82" s="10" t="n">
         <v>0</v>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E84" s="10" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D88" s="10" t="n">
         <v>0</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D90" s="10" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D92" s="10" t="n">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D94" s="10" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>0</v>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E96" s="10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>0</v>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E98" s="10" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>0</v>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E100" s="10" t="n">
         <v>0</v>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D103" s="7" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D104" s="10" t="n">
         <v>0</v>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D106" s="10" t="n">
         <v>0</v>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D108" s="10" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D110" s="10" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D112" s="10" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C113" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="E114" s="10" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="C115" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>0</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D116" s="10" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="C117" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D118" s="10" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>0</v>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E120" s="10" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D122" s="10" t="n">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>0</v>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E124" s="10" t="n">
         <v>0</v>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="E125" s="7" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D126" s="10" t="n">
         <v>0</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D128" s="10" t="n">
         <v>0</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="C129" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E129" s="7" t="n">
         <v>0</v>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E130" s="10" t="n">
         <v>0</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="C131" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E131" s="7" t="n">
         <v>0</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E132" s="10" t="n">
         <v>0</v>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="C133" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E133" s="7" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D134" s="10" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="C135" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>0</v>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E136" s="10" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="C137" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E139" s="7" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D140" s="10" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C141" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>0</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D142" s="10" t="n">
         <v>0</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>0</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D144" s="10" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="C145" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D145" s="7" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D146" s="10" t="n">
         <v>0</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D148" s="10" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C149" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D149" s="7" t="n">
         <v>0</v>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D150" s="10" t="n">
         <v>0</v>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="C151" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E151" s="7" t="n">
         <v>0</v>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D152" s="10" t="n">
         <v>0</v>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>0</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E156" s="10" t="n">
         <v>0</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C157" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="E157" s="7" t="n">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D158" s="10" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
         <v>7264</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>7264</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>7264</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>7264</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>7264</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>7264</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -1051,7 +1051,7 @@
         <v>7264</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>7264</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>7264</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>0</v>
@@ -1201,7 +1201,7 @@
         <v>7168</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0</v>
@@ -1226,7 +1226,7 @@
         <v>7168</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>7168</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
@@ -1351,7 +1351,7 @@
         <v>7168</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7168</v>
+        <v>0</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>7168</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>7168</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>7168</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>7168</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>7168</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>7168</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>7168</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>7168</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>7264</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>7168</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>7264</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="D58" s="10" t="n">
         <v>3680</v>
@@ -1926,7 +1926,7 @@
         <v>7360</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>7360</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E65" s="7" t="n">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>7360</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>7360</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>7360</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>7360</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>7360</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E77" s="7" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
         <v>7360</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>7456</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E82" s="10" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>3728</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E84" s="10" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>7456</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>7456</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
         <v>7456</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>7456</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>7456</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>7456</v>
+        <v>0</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>0</v>
@@ -3051,7 +3051,7 @@
         <v>7456</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E104" s="10" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>7456</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>7456</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E108" s="10" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>7456</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>7456</v>
+        <v>3728</v>
       </c>
       <c r="E114" s="10" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>7456</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>7456</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>7456</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E121" s="7" t="n">
         <v>0</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>0</v>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="E125" s="7" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
         <v>7360</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E126" s="10" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         <v>7456</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>7360</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E128" s="10" t="n">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>7360</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E133" s="7" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>7360</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E136" s="10" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         <v>7360</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>0</v>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
         <v>7264</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E148" s="10" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C149" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="D149" s="7" t="n">
         <v>0</v>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E152" s="10" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>7264</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>7264</v>
       </c>
       <c r="D155" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E155" s="7" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>7264</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="E157" s="7" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
         <v>7264</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E158" s="10" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>3632</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>0</v>
@@ -629,7 +629,7 @@
         <v>3632</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>3632</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>0</v>
@@ -679,7 +679,7 @@
         <v>3632</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>3584</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>3680</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F76" s="10" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>3680</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F128" s="10" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>3680</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F130" s="10" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>3680</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F132" s="10" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:37</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="6">
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="39">
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="43">
@@ -2610,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="87">
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="88">
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="92">
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="94">
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="103">

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:37</t>
+          <t>2026-06-08 18:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Trips_Pricing_All" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:47</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2682,10 +2682,10 @@
         <v>0</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="90">
@@ -2694,14 +2694,14 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="91">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C91" s="7" t="n">
@@ -2735,32 +2735,32 @@
         <v>0</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="D92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="10" t="n">
         <v>3728</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2794,14 +2794,14 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>0</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
@@ -2890,11 +2890,11 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C99" s="7" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
@@ -2969,23 +2969,23 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="7" t="n">
         <v>3728</v>
-      </c>
-      <c r="E101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3019,14 +3019,14 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>0</v>
@@ -3040,18 +3040,18 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E104" s="10" t="n">
         <v>0</v>
@@ -3094,14 +3094,14 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E106" s="10" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
@@ -3176,7 +3176,7 @@
         <v>7456</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>0</v>
@@ -3190,18 +3190,18 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E110" s="10" t="n">
         <v>0</v>
@@ -3219,14 +3219,14 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C111" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>0</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C113" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E113" s="7" t="n">
         <v>0</v>
@@ -3319,14 +3319,14 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C115" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C117" s="7" t="n">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
         <v>7456</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E118" s="10" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C119" s="7" t="n">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C121" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E121" s="7" t="n">
         <v>0</v>
@@ -3490,18 +3490,18 @@
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E122" s="10" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C123" s="7" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
@@ -3594,14 +3594,14 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E126" s="10" t="n">
         <v>0</v>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F127" s="7" t="n">
         <v>0</v>
@@ -3640,11 +3640,11 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
@@ -3654,7 +3654,7 @@
         <v>3680</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="F128" s="10" t="n">
         <v>0</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C129" s="7" t="n">
@@ -3679,7 +3679,7 @@
         <v>3680</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F129" s="7" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
@@ -3704,7 +3704,7 @@
         <v>3680</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="F130" s="10" t="n">
         <v>0</v>
@@ -3715,11 +3715,11 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C131" s="7" t="n">
@@ -3729,7 +3729,7 @@
         <v>3680</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F131" s="7" t="n">
         <v>0</v>
@@ -3744,17 +3744,17 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="F132" s="10" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C135" s="7" t="n">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C137" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E137" s="7" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
@@ -3915,18 +3915,18 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C139" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E139" s="7" t="n">
         <v>0</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C141" s="7" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
@@ -4094,11 +4094,11 @@
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="D146" s="10" t="n">
         <v>0</v>
@@ -4115,18 +4115,18 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C147" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>0</v>
@@ -4144,14 +4144,14 @@
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E148" s="10" t="n">
         <v>0</v>
@@ -4194,14 +4194,14 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E150" s="10" t="n">
         <v>0</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
@@ -4240,18 +4240,18 @@
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E152" s="10" t="n">
         <v>0</v>
@@ -4294,14 +4294,14 @@
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E154" s="10" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C155" s="7" t="n">
@@ -4344,14 +4344,14 @@
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E156" s="10" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>7264</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E157" s="7" t="n">
         <v>0</v>
@@ -4388,33 +4388,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B158" s="9" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C158" s="10" t="n">
-        <v>7264</v>
-      </c>
-      <c r="D158" s="10" t="n">
-        <v>3632</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G158"/>
+  <autoFilter ref="A4:G157"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Trips_Pricing_All" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trips_Pricing_All'!$A$4:$G$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C137" s="7" t="n">
@@ -3890,18 +3890,18 @@
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
         <v>7360</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C141" s="7" t="n">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C143" s="7" t="n">
@@ -4069,11 +4069,11 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C145" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="D145" s="7" t="n">
         <v>0</v>
@@ -4090,18 +4090,18 @@
     </row>
     <row r="146">
       <c r="A146" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
         <v>7264</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E146" s="10" t="n">
         <v>0</v>
@@ -4119,14 +4119,14 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C147" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>0</v>
@@ -4169,14 +4169,14 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C149" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E149" s="7" t="n">
         <v>0</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
@@ -4215,18 +4215,18 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E151" s="7" t="n">
         <v>0</v>
@@ -4269,14 +4269,14 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C153" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C155" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D155" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E155" s="7" t="n">
         <v>0</v>
@@ -4351,7 +4351,7 @@
         <v>7264</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E156" s="10" t="n">
         <v>0</v>
@@ -4363,33 +4363,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="5" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C157" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="D157" s="7" t="n">
-        <v>3632</v>
-      </c>
-      <c r="E157" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G157"/>
+  <autoFilter ref="A4:G156"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/15_Trips_Pricing_All.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>
